--- a/public/lab/regulation.xlsx
+++ b/public/lab/regulation.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="320">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -599,6 +599,9 @@
   </si>
   <si>
     <t xml:space="preserve">Products with vegetable fats must be called ‘milk-containing product with milk fat substitute’ (spread, cheese product, etc.), not butter or cheese.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://adilet.zan.kz/rus/docs/H13EV000067</t>
   </si>
   <si>
     <t xml:space="preserve">Запрет / ограничение состава</t>
@@ -2925,8 +2928,8 @@
       <c r="K10" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>92</v>
+      <c r="L10" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2940,31 +2943,31 @@
         <v>75</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2984,25 +2987,25 @@
         <v>124</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3016,31 +3019,31 @@
         <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3060,25 +3063,25 @@
         <v>124</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3092,31 +3095,31 @@
         <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>148</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3136,25 +3139,25 @@
         <v>124</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3168,31 +3171,31 @@
         <v>80</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>156</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3212,25 +3215,25 @@
         <v>156</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3244,31 +3247,31 @@
         <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>148</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3291,22 +3294,22 @@
         <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3329,22 +3332,22 @@
         <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3358,31 +3361,31 @@
         <v>91</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3396,31 +3399,31 @@
         <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3434,31 +3437,31 @@
         <v>101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>156</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3472,31 +3475,31 @@
         <v>101</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>148</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3516,25 +3519,25 @@
         <v>124</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3548,22 +3551,23 @@
     <hyperlink ref="L7" r:id="rId6" display="https://eec.eaeunion.org/comission/department/deptexreg/tr/PischevkaMarkirovka.php"/>
     <hyperlink ref="L8" r:id="rId7" display="https://nkprom.ru/news/v-tr-ts-022-2011-pishchevaya-produktsiya-v-chasti-ee-markirovki-i-tr-ts-022-2011-o-bezopasnosti-sred/"/>
     <hyperlink ref="L9" r:id="rId8" display="https://foodsmi.com/zakonodatelstvo/izmeneniya-v-tekhreglamente-na-maslozhirovuyu-produktsiyu/"/>
-    <hyperlink ref="L11" r:id="rId9" display="https://biz.ligazakon.net/news/231710_prezident-pdpisav-zakon-pro-obmezhennya-vikoristannya-palmovo-ol-u-produktakh-kharchuvannya"/>
-    <hyperlink ref="L12" r:id="rId10" display="https://ngu.com.ua/palmova-oliia-shkoda-sklad-doza-i-etyketka/"/>
-    <hyperlink ref="L13" r:id="rId11" display="https://ansa.gov.md/sites/default/files/documents/Ordine/Ordin%20nr.%20369.pdf"/>
-    <hyperlink ref="L14" r:id="rId12" display="https://www.retail.ru/news/v-rossii-poyavilsya-edinyy-katalog-produktov-bez-palmy-23-dekabrya-2025-272975/"/>
-    <hyperlink ref="L15" r:id="rId13" display="https://www.klerk.ru/buh/articles/713288/"/>
-    <hyperlink ref="L16" r:id="rId14" display="https://www.gazeta.ru/business/2019/07/01/12467725.shtml"/>
-    <hyperlink ref="L17" r:id="rId15" display="https://oleoscope.com/analytics/gosduma-predlozhila-markirovku-dlja-masla/"/>
-    <hyperlink ref="L18" r:id="rId16" display="https://ria.ru/20260722/markirovka-2106133235.html"/>
-    <hyperlink ref="L19" r:id="rId17" display="https://inbusiness.kz/ru/news/v-kazahstane-pochti-vdvoe-rasshirili-markirovku-tovarov"/>
-    <hyperlink ref="L20" r:id="rId18" display="https://kapital.kz/business/134274/maslopererabotchiki-rk-vystupayut-za-ukazaniye-nalichiya-v-produktakh-pal-movogo-masla.html"/>
-    <hyperlink ref="L21" r:id="rId19" display="https://dairynews.today/kz/news/v-kyrgyzstane-obsuzhdayut-ispolzovanie-palmovogo-masla-v-proizvodstve-moloka.html"/>
-    <hyperlink ref="L22" r:id="rId20" display="https://base.spinform.ru/show_doc.fwx?rgn=124770"/>
-    <hyperlink ref="L23" r:id="rId21" display="https://podrobno.uz/cat/obchestvo/v-uzbekistane-vvodyat-obyazatelnyy-laboratornyy-kontrol-palmovogo-masla-i-transzhirov/"/>
-    <hyperlink ref="L24" r:id="rId22" display="https://www.spot.uz/ru/2026/07/30/palm-oil"/>
-    <hyperlink ref="L25" r:id="rId23" display="https://vzglyad.uz/2026/10/09/obsuzhdenie-poryadka-markirovki-rastitelnogo-masla"/>
-    <hyperlink ref="L26" r:id="rId24" display="https://dairynews.today/kz/news/armenia-to-enforce-stricter-labeling-rules-for-dairy-and-meat-products.html"/>
+    <hyperlink ref="L10" r:id="rId9" display="https://adilet.zan.kz/rus/docs/H13EV000067"/>
+    <hyperlink ref="L11" r:id="rId10" display="https://biz.ligazakon.net/news/231710_prezident-pdpisav-zakon-pro-obmezhennya-vikoristannya-palmovo-ol-u-produktakh-kharchuvannya"/>
+    <hyperlink ref="L12" r:id="rId11" display="https://ngu.com.ua/palmova-oliia-shkoda-sklad-doza-i-etyketka/"/>
+    <hyperlink ref="L13" r:id="rId12" display="https://ansa.gov.md/sites/default/files/documents/Ordine/Ordin%20nr.%20369.pdf"/>
+    <hyperlink ref="L14" r:id="rId13" display="https://www.retail.ru/news/v-rossii-poyavilsya-edinyy-katalog-produktov-bez-palmy-23-dekabrya-2025-272975/"/>
+    <hyperlink ref="L15" r:id="rId14" display="https://www.klerk.ru/buh/articles/713288/"/>
+    <hyperlink ref="L16" r:id="rId15" display="https://www.gazeta.ru/business/2019/07/01/12467725.shtml"/>
+    <hyperlink ref="L17" r:id="rId16" display="https://oleoscope.com/analytics/gosduma-predlozhila-markirovku-dlja-masla/"/>
+    <hyperlink ref="L18" r:id="rId17" display="https://ria.ru/20260722/markirovka-2106133235.html"/>
+    <hyperlink ref="L19" r:id="rId18" display="https://inbusiness.kz/ru/news/v-kazahstane-pochti-vdvoe-rasshirili-markirovku-tovarov"/>
+    <hyperlink ref="L20" r:id="rId19" display="https://kapital.kz/business/134274/maslopererabotchiki-rk-vystupayut-za-ukazaniye-nalichiya-v-produktakh-pal-movogo-masla.html"/>
+    <hyperlink ref="L21" r:id="rId20" display="https://dairynews.today/kz/news/v-kyrgyzstane-obsuzhdayut-ispolzovanie-palmovogo-masla-v-proizvodstve-moloka.html"/>
+    <hyperlink ref="L22" r:id="rId21" display="https://base.spinform.ru/show_doc.fwx?rgn=124770"/>
+    <hyperlink ref="L23" r:id="rId22" display="https://podrobno.uz/cat/obchestvo/v-uzbekistane-vvodyat-obyazatelnyy-laboratornyy-kontrol-palmovogo-masla-i-transzhirov/"/>
+    <hyperlink ref="L24" r:id="rId23" display="https://www.spot.uz/ru/2026/07/30/palm-oil"/>
+    <hyperlink ref="L25" r:id="rId24" display="https://vzglyad.uz/2026/10/09/obsuzhdenie-poryadka-markirovki-rastitelnogo-masla"/>
+    <hyperlink ref="L26" r:id="rId25" display="https://dairynews.today/kz/news/armenia-to-enforce-stricter-labeling-rules-for-dairy-and-meat-products.html"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3572,7 +3576,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId26"/>
 </worksheet>
 </file>
 
@@ -3590,32 +3594,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="12"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3624,7 +3628,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="12"/>
     </row>
@@ -3652,7 +3656,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="12"/>
     </row>
@@ -3670,7 +3674,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B14" s="12"/>
     </row>
@@ -3682,19 +3686,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B18" s="12"/>
     </row>
@@ -3716,26 +3720,26 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/public/lab/regulation.xlsx
+++ b/public/lab/regulation.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Справочник" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Меры!$A$1:$L$26</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Меры!$A$1:$L$29</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Сводка по странам'!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="341">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -496,54 +496,54 @@
     <t xml:space="preserve">https://vinciworks.com/blog/eudr-delayed-again-what-changed-what-is-now-fixed-and-what-businesses-should-do-in-2026/</t>
   </si>
   <si>
+    <t xml:space="preserve">30.12.2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Делегированный регламент (ЕС) 2026/2102 от 13.07.2026 (ОЖ 17.09.2026), изм. прил. I к EUDR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расширение EUDR на производные пальмового масла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принят и вступил в силу 18.09.2026. В перечень EUDR добавлены производные масличной пальмы: гидрогенизированные и химически модифицированные пальмовые масла (ex 1516 20, ex 1518), сырой глицерин, жирные спирты и кислоты и их эфиры, амины, мыло (ex 3401), химические препараты (ex 3824 99), полиэфиры. Новые позиции применяются с 30.12.2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUDR extended to palm oil derivatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adopted; in force since 18 Sep 2026. Adds oil-palm derivatives to the EUDR list: hydrogenated and chemically modified palm oils (ex 1516 20, ex 1518), crude glycerol, fatty alcohols, acids and esters, amines, soap (ex 3401), chemical preparations (ex 3824 99), polyethers. New entries apply from 30 Dec 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://eur-lex.europa.eu/eli/reg_del/2026/2102/oj/eng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕАЭС (общие нормы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.07.2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТР ТС 022/2011 «Пищевая продукция в части её маркировки»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допускается общее название «масло растительное»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рафинированные масла можно указывать в составе как «масло (жир) растительное» без вида — главная лазейка, позволяющая не называть пальмовое масло.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic ‘vegetable oil’ name allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refined oils may be listed as ‘vegetable oil (fat)’ without the species — the main loophole for not naming palm oil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://eec.eaeunion.org/comission/department/deptexreg/tr/PischevkaMarkirovka.php</t>
+  </si>
+  <si>
     <t xml:space="preserve">Предложение / проект</t>
   </si>
   <si>
-    <t xml:space="preserve">04.05.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проект делегированного акта к EUDR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Расширение EUDR на производные пальмового масла</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Еврокомиссия предложила включить олеохимию (жирные кислоты, их эфиры, мыло на пальмовом масле).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EUDR extended to palm oil derivatives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Commission proposed adding oleochemicals (fatty acids, their esters, palm-based soap).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://blog.foodsconnected.com/7-key-takeaways-from-the-april-2026-eudr-review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЕАЭС (общие нормы)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.07.2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТР ТС 022/2011 «Пищевая продукция в части её маркировки»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Допускается общее название «масло растительное»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рафинированные масла можно указывать в составе как «масло (жир) растительное» без вида — главная лазейка, позволяющая не называть пальмовое масло.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic ‘vegetable oil’ name allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refined oils may be listed as ‘vegetable oil (fat)’ without the species — the main loophole for not naming palm oil.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://eec.eaeunion.org/comission/department/deptexreg/tr/PischevkaMarkirovka.php</t>
-  </si>
-  <si>
     <t xml:space="preserve">Изменения в ТР ТС 022/2011 (разработчик — Беларусь)</t>
   </si>
   <si>
@@ -583,6 +583,27 @@
     <t xml:space="preserve">https://foodsmi.com/zakonodatelstvo/izmeneniya-v-tekhreglamente-na-maslozhirovuyu-produktsiyu/</t>
   </si>
   <si>
+    <t xml:space="preserve">28.12.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решение Коллегии ЕЭК от 29.06.2026 № 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новые перечни стандартов к ТР ТС 024/2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утверждены перечень стандартов, добровольное применение которых обеспечивает соблюдение ТР ТС 024/2011 на масложировую продукцию (50 позиций), и перечень методов испытаний и отбора проб (183 позиции). Заменяет решение Коллегии ЕЭК № 53 от 29.03.2022. Вступает в силу через 180 дней после опубликования — 28.12.2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New lists of standards for TR CU 024/2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approves the list of standards whose voluntary use ensures compliance with TR CU 024/2011 on oil and fat products (50 items) and the list of test and sampling methods (183 items). Replaces EEC Board Decision No. 53 of 29 Mar 2022. Enters into force 180 days after publication — 28 Dec 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://base.spinform.ru/show_doc.fwx?rgn=177646</t>
+  </si>
+  <si>
     <t xml:space="preserve">Молочка и заменители молочного жира</t>
   </si>
   <si>
@@ -691,6 +712,30 @@
     <t xml:space="preserve">https://www.retail.ru/news/v-rossii-poyavilsya-edinyy-katalog-produktov-bez-palmy-23-dekabrya-2025-272975/</t>
   </si>
   <si>
+    <t xml:space="preserve">Налоги</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.10.2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Федеральный закон от 02.08.2019 № 268-ФЗ (ст. 164 НК РФ); Постановление Правительства РФ от 11.05.2022 № 849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НДС 20% на пальмовое масло вместо льготных 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пальмовое масло исключено из перечня продовольствия с льготной ставкой НДС 10% с 01.10.2019; с 01.07.2022 ставка 20% распространена и на фракции пальмового масла (при ввозе и реализации).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% VAT on palm oil instead of reduced 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palm oil removed from the list of foods with the reduced 10% VAT rate from 1 Oct 2019; from 1 Jul 2022 the 20% rate also applies to palm oil fractions (on import and sale).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.v2b.ru/documents/federalnyy-zakon-ot-02-08-2019-268-fz/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Цифровая маркировка и прослеживаемость</t>
   </si>
   <si>
@@ -778,6 +823,27 @@
     <t xml:space="preserve">https://ria.ru/20260722/markirovka-2106133235.html</t>
   </si>
   <si>
+    <t xml:space="preserve">22.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выступление В. Володина на пленарном заседании Госдумы 22.10.2026; предложение С. Миронова 24.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запрет пальмового масла в детском питании и в закупках школ и больниц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Председатель Госдумы предложил обсудить запрет пальмового масла в детских продуктах и повышение его налогообложения. Лидер фракции «Справедливая Россия» предложил отдельным федеральным законом запретить медицинским и образовательным учреждениям закупать продукты с пальмовым маслом. Законопроект не внесён.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palm oil ban in baby food and in school/hospital procurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The State Duma speaker proposed discussing a ban on palm oil in children’s food and higher taxation of palm oil. The A Just Russia faction leader proposed a federal law banning medical and educational institutions from buying food containing palm oil. No bill has been introduced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ria.ru/20261024/maslo-2126771171.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">01.04.2027</t>
   </si>
   <si>
@@ -877,9 +943,6 @@
     <t xml:space="preserve">https://podrobno.uz/cat/obchestvo/v-uzbekistane-vvodyat-obyazatelnyy-laboratornyy-kontrol-palmovogo-masla-i-transzhirov/</t>
   </si>
   <si>
-    <t xml:space="preserve">Налоги</t>
-  </si>
-  <si>
     <t xml:space="preserve">30.07.2026</t>
   </si>
   <si>
@@ -955,7 +1018,7 @@
     <t xml:space="preserve">Данные на</t>
   </si>
   <si>
-    <t xml:space="preserve">23.10.2026</t>
+    <t xml:space="preserve">26.10.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Период обзора</t>
@@ -1603,20 +1666,20 @@
         <v>16</v>
       </c>
       <c r="F2" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L2)+COUNTIF(Меры!$B$2:$B$26,M2)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L2)+COUNTIF(Меры!$B$2:$B$29,M2)</f>
         <v>5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L2,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M2,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L2,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M2,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H2" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L2,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M2,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L2,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M2,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I2" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L2,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M2,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L2,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M2,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
@@ -1648,20 +1711,20 @@
         <v>16</v>
       </c>
       <c r="F3" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L3)+COUNTIF(Меры!$B$2:$B$26,M3)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L3)+COUNTIF(Меры!$B$2:$B$29,M3)</f>
         <v>5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L3,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M3,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L3,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M3,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H3" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L3,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M3,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L3,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M3,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I3" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L3,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M3,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L3,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M3,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>17</v>
@@ -1693,20 +1756,20 @@
         <v>27</v>
       </c>
       <c r="F4" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L4)+COUNTIF(Меры!$B$2:$B$26,M4)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L4)+COUNTIF(Меры!$B$2:$B$29,M4)</f>
         <v>5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L4,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M4,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L4,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M4,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H4" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L4,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M4,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L4,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M4,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I4" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L4,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M4,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L4,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M4,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>28</v>
@@ -1738,20 +1801,20 @@
         <v>33</v>
       </c>
       <c r="F5" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L5)+COUNTIF(Меры!$B$2:$B$26,M5)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L5)+COUNTIF(Меры!$B$2:$B$29,M5)</f>
         <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L5,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M5,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L5,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M5,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H5" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L5,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M5,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L5,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M5,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L5,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M5,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L5,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M5,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -1783,20 +1846,20 @@
         <v>27</v>
       </c>
       <c r="F6" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L6)+COUNTIF(Меры!$B$2:$B$26,M6)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L6)+COUNTIF(Меры!$B$2:$B$29,M6)</f>
         <v>5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L6,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M6,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L6,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M6,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H6" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L6,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M6,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L6,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M6,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I6" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L6,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M6,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L6,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M6,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -1828,20 +1891,20 @@
         <v>43</v>
       </c>
       <c r="F7" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L7)+COUNTIF(Меры!$B$2:$B$26,M7)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L7)+COUNTIF(Меры!$B$2:$B$29,M7)</f>
         <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L7,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M7,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L7,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M7,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H7" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L7,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M7,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L7,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M7,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L7,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M7,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L7,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M7,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -1873,20 +1936,20 @@
         <v>43</v>
       </c>
       <c r="F8" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L8)+COUNTIF(Меры!$B$2:$B$26,M8)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L8)+COUNTIF(Меры!$B$2:$B$29,M8)</f>
         <v>5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L8,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M8,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L8,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M8,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L8,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M8,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L8,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M8,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L8,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M8,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L8,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M8,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -1918,20 +1981,20 @@
         <v>33</v>
       </c>
       <c r="F9" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L9)+COUNTIF(Меры!$B$2:$B$26,M9)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L9)+COUNTIF(Меры!$B$2:$B$29,M9)</f>
         <v>5</v>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L9,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M9,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L9,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M9,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H9" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L9,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M9,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L9,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M9,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L9,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M9,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L9,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M9,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -1963,20 +2026,20 @@
         <v>33</v>
       </c>
       <c r="F10" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L10)+COUNTIF(Меры!$B$2:$B$26,M10)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L10)+COUNTIF(Меры!$B$2:$B$29,M10)</f>
         <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L10,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M10,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L10,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M10,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L10,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M10,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L10,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M10,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I10" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L10,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M10,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L10,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M10,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -2008,20 +2071,20 @@
         <v>33</v>
       </c>
       <c r="F11" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L11)+COUNTIF(Меры!$B$2:$B$26,M11)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L11)+COUNTIF(Меры!$B$2:$B$29,M11)</f>
         <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L11,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M11,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L11,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M11,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H11" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L11,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M11,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L11,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M11,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L11,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M11,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L11,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M11,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -2053,19 +2116,19 @@
         <v>43</v>
       </c>
       <c r="F12" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L12)+COUNTIF(Меры!$B$2:$B$26,M12)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L12)+COUNTIF(Меры!$B$2:$B$29,M12)</f>
+        <v>5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L12,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M12,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L12,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M12,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L12,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M12,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L12,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M12,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L12,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M12,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L12,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M12,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
@@ -2098,19 +2161,19 @@
         <v>33</v>
       </c>
       <c r="F13" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L13)+COUNTIF(Меры!$B$2:$B$26,M13)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L13)+COUNTIF(Меры!$B$2:$B$29,M13)</f>
         <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L13,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M13,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L13,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M13,Меры!$E$2:$E$29,"Действует")</f>
         <v>1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L13,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M13,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L13,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M13,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
         <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L13,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M13,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L13,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M13,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -2143,19 +2206,19 @@
         <v>27</v>
       </c>
       <c r="F14" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L14)+COUNTIF(Меры!$B$2:$B$26,M14)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L14)+COUNTIF(Меры!$B$2:$B$29,M14)</f>
         <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L14,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M14,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L14,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M14,Меры!$E$2:$E$29,"Действует")</f>
         <v>2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L14,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M14,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L14,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M14,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
         <v>0</v>
       </c>
       <c r="I14" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L14,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M14,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L14,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M14,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
@@ -2188,20 +2251,20 @@
         <v>16</v>
       </c>
       <c r="F15" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L15)+COUNTIF(Меры!$B$2:$B$26,M15)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L15)+COUNTIF(Меры!$B$2:$B$29,M15)</f>
+        <v>12</v>
       </c>
       <c r="G15" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L15,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M15,Меры!$E$2:$E$26,"Действует")</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L15,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M15,Меры!$E$2:$E$29,"Действует")</f>
+        <v>6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L15,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M15,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L15,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M15,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L15,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M15,Меры!$E$2:$E$26,"Предложение / проект")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L15,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M15,Меры!$E$2:$E$29,"Предложение / проект")</f>
+        <v>4</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>81</v>
@@ -2233,19 +2296,19 @@
         <v>33</v>
       </c>
       <c r="F16" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L16)+COUNTIF(Меры!$B$2:$B$26,M16)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L16)+COUNTIF(Меры!$B$2:$B$29,M16)</f>
+        <v>7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L16,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M16,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L16,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M16,Меры!$E$2:$E$29,"Действует")</f>
         <v>3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L16,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M16,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L16,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M16,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L16,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M16,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L16,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M16,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>2</v>
       </c>
       <c r="J16" s="2" t="s">
@@ -2278,19 +2341,19 @@
         <v>33</v>
       </c>
       <c r="F17" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L17)+COUNTIF(Меры!$B$2:$B$26,M17)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L17)+COUNTIF(Меры!$B$2:$B$29,M17)</f>
+        <v>6</v>
       </c>
       <c r="G17" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L17,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M17,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L17,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M17,Меры!$E$2:$E$29,"Действует")</f>
         <v>4</v>
       </c>
       <c r="H17" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L17,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M17,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L17,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M17,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L17,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M17,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L17,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M17,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>1</v>
       </c>
       <c r="J17" s="2" t="s">
@@ -2323,19 +2386,19 @@
         <v>93</v>
       </c>
       <c r="F18" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L18)+COUNTIF(Меры!$B$2:$B$26,M18)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L18)+COUNTIF(Меры!$B$2:$B$29,M18)</f>
         <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L18,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M18,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L18,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M18,Меры!$E$2:$E$29,"Действует")</f>
         <v>1</v>
       </c>
       <c r="H18" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L18,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M18,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L18,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M18,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
         <v>0</v>
       </c>
       <c r="I18" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L18,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M18,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L18,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M18,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>0</v>
       </c>
       <c r="J18" s="2" t="s">
@@ -2368,19 +2431,19 @@
         <v>43</v>
       </c>
       <c r="F19" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L19)+COUNTIF(Меры!$B$2:$B$26,M19)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L19)+COUNTIF(Меры!$B$2:$B$29,M19)</f>
         <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L19,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M19,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L19,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M19,Меры!$E$2:$E$29,"Действует")</f>
         <v>0</v>
       </c>
       <c r="H19" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L19,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M19,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L19,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M19,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
         <v>0</v>
       </c>
       <c r="I19" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L19,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M19,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L19,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M19,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>0</v>
       </c>
       <c r="J19" s="2" t="s">
@@ -2413,19 +2476,19 @@
         <v>33</v>
       </c>
       <c r="F20" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L20)+COUNTIF(Меры!$B$2:$B$26,M20)</f>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L20)+COUNTIF(Меры!$B$2:$B$29,M20)</f>
         <v>3</v>
       </c>
       <c r="G20" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L20,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M20,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L20,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M20,Меры!$E$2:$E$29,"Действует")</f>
         <v>1</v>
       </c>
       <c r="H20" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L20,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M20,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L20,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M20,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
         <v>1</v>
       </c>
       <c r="I20" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L20,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M20,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L20,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M20,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>1</v>
       </c>
       <c r="J20" s="2" t="s">
@@ -2458,19 +2521,19 @@
         <v>33</v>
       </c>
       <c r="F21" s="4" t="n">
-        <f aca="false">COUNTIF(Меры!$B$2:$B$26,L21)+COUNTIF(Меры!$B$2:$B$26,M21)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(Меры!$B$2:$B$29,L21)+COUNTIF(Меры!$B$2:$B$29,M21)</f>
+        <v>6</v>
       </c>
       <c r="G21" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L21,Меры!$E$2:$E$26,"Действует")+COUNTIFS(Меры!$B$2:$B$26,M21,Меры!$E$2:$E$26,"Действует")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L21,Меры!$E$2:$E$29,"Действует")+COUNTIFS(Меры!$B$2:$B$29,M21,Меры!$E$2:$E$29,"Действует")</f>
         <v>4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L21,Меры!$E$2:$E$26,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$26,M21,Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L21,Меры!$E$2:$E$29,"Принято, вступает позже")+COUNTIFS(Меры!$B$2:$B$29,M21,Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>1</v>
       </c>
       <c r="I21" s="4" t="n">
-        <f aca="false">COUNTIFS(Меры!$B$2:$B$26,L21,Меры!$E$2:$E$26,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$26,M21,Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIFS(Меры!$B$2:$B$29,L21,Меры!$E$2:$E$29,"Предложение / проект")+COUNTIFS(Меры!$B$2:$B$29,M21,Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>1</v>
       </c>
       <c r="J21" s="2" t="s">
@@ -2491,19 +2554,19 @@
         <v>109</v>
       </c>
       <c r="F23" s="5" t="n">
-        <f aca="false">COUNTA(Меры!$A$2:$A$26)</f>
-        <v>25</v>
+        <f aca="false">COUNTA(Меры!$A$2:$A$29)</f>
+        <v>28</v>
       </c>
       <c r="G23" s="5" t="n">
-        <f aca="false">COUNTIF(Меры!$E$2:$E$26,"Действует")</f>
-        <v>15</v>
+        <f aca="false">COUNTIF(Меры!$E$2:$E$29,"Действует")</f>
+        <v>16</v>
       </c>
       <c r="H23" s="5" t="n">
-        <f aca="false">COUNTIF(Меры!$E$2:$E$26,"Принято, вступает позже")</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Меры!$E$2:$E$29,"Принято, вступает позже")</f>
+        <v>6</v>
       </c>
       <c r="I23" s="5" t="n">
-        <f aca="false">COUNTIF(Меры!$E$2:$E$26,"Предложение / проект")</f>
+        <f aca="false">COUNTIF(Меры!$E$2:$E$29,"Предложение / проект")</f>
         <v>6</v>
       </c>
     </row>
@@ -2536,7 +2599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2742,7 +2805,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -2755,29 +2818,29 @@
       <c r="D6" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2788,7 +2851,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>123</v>
@@ -2797,25 +2860,25 @@
         <v>124</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="8" t="s">
         <v>170</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2826,13 +2889,13 @@
         <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>92</v>
@@ -2864,7 +2927,7 @@
         <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>177</v>
@@ -2894,7 +2957,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -2902,16 +2965,16 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>186</v>
@@ -2932,15 +2995,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>192</v>
@@ -2949,28 +3012,28 @@
         <v>124</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -2981,83 +3044,83 @@
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>124</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="L13" s="8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>124</v>
@@ -3095,34 +3158,34 @@
         <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -3133,7 +3196,7 @@
         <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>124</v>
@@ -3160,7 +3223,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -3171,34 +3234,34 @@
         <v>80</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>156</v>
+        <v>236</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -3209,69 +3272,69 @@
         <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>156</v>
+        <v>192</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>148</v>
+        <v>199</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3279,171 +3342,171 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>123</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>124</v>
+        <v>199</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>124</v>
+        <v>236</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>276</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>156</v>
+        <v>192</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>285</v>
@@ -3464,21 +3527,21 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>148</v>
+        <v>213</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>291</v>
@@ -3502,18 +3565,18 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>124</v>
@@ -3540,34 +3603,151 @@
         <v>304</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L29"/>
   <hyperlinks>
     <hyperlink ref="L2" r:id="rId1" display="https://eur-lex.europa.eu/eli/reg/2011/1169/oj"/>
     <hyperlink ref="L3" r:id="rId2" display="https://eur-lex.europa.eu/eli/dir/2019/2161/oj"/>
     <hyperlink ref="L4" r:id="rId3" display="https://eur-lex.europa.eu/eli/dir/2024/825/oj"/>
     <hyperlink ref="L5" r:id="rId4" display="https://vinciworks.com/blog/eudr-delayed-again-what-changed-what-is-now-fixed-and-what-businesses-should-do-in-2026/"/>
-    <hyperlink ref="L6" r:id="rId5" display="https://blog.foodsconnected.com/7-key-takeaways-from-the-april-2026-eudr-review"/>
+    <hyperlink ref="L6" r:id="rId5" display="https://eur-lex.europa.eu/eli/reg_del/2026/2102/oj/eng"/>
     <hyperlink ref="L7" r:id="rId6" display="https://eec.eaeunion.org/comission/department/deptexreg/tr/PischevkaMarkirovka.php"/>
     <hyperlink ref="L8" r:id="rId7" display="https://nkprom.ru/news/v-tr-ts-022-2011-pishchevaya-produktsiya-v-chasti-ee-markirovki-i-tr-ts-022-2011-o-bezopasnosti-sred/"/>
     <hyperlink ref="L9" r:id="rId8" display="https://foodsmi.com/zakonodatelstvo/izmeneniya-v-tekhreglamente-na-maslozhirovuyu-produktsiyu/"/>
-    <hyperlink ref="L10" r:id="rId9" display="https://adilet.zan.kz/rus/docs/H13EV000067"/>
-    <hyperlink ref="L11" r:id="rId10" display="https://biz.ligazakon.net/news/231710_prezident-pdpisav-zakon-pro-obmezhennya-vikoristannya-palmovo-ol-u-produktakh-kharchuvannya"/>
-    <hyperlink ref="L12" r:id="rId11" display="https://ngu.com.ua/palmova-oliia-shkoda-sklad-doza-i-etyketka/"/>
-    <hyperlink ref="L13" r:id="rId12" display="https://ansa.gov.md/sites/default/files/documents/Ordine/Ordin%20nr.%20369.pdf"/>
-    <hyperlink ref="L14" r:id="rId13" display="https://www.retail.ru/news/v-rossii-poyavilsya-edinyy-katalog-produktov-bez-palmy-23-dekabrya-2025-272975/"/>
-    <hyperlink ref="L15" r:id="rId14" display="https://www.klerk.ru/buh/articles/713288/"/>
-    <hyperlink ref="L16" r:id="rId15" display="https://www.gazeta.ru/business/2019/07/01/12467725.shtml"/>
-    <hyperlink ref="L17" r:id="rId16" display="https://oleoscope.com/analytics/gosduma-predlozhila-markirovku-dlja-masla/"/>
-    <hyperlink ref="L18" r:id="rId17" display="https://ria.ru/20260722/markirovka-2106133235.html"/>
-    <hyperlink ref="L19" r:id="rId18" display="https://inbusiness.kz/ru/news/v-kazahstane-pochti-vdvoe-rasshirili-markirovku-tovarov"/>
-    <hyperlink ref="L20" r:id="rId19" display="https://kapital.kz/business/134274/maslopererabotchiki-rk-vystupayut-za-ukazaniye-nalichiya-v-produktakh-pal-movogo-masla.html"/>
-    <hyperlink ref="L21" r:id="rId20" display="https://dairynews.today/kz/news/v-kyrgyzstane-obsuzhdayut-ispolzovanie-palmovogo-masla-v-proizvodstve-moloka.html"/>
-    <hyperlink ref="L22" r:id="rId21" display="https://base.spinform.ru/show_doc.fwx?rgn=124770"/>
-    <hyperlink ref="L23" r:id="rId22" display="https://podrobno.uz/cat/obchestvo/v-uzbekistane-vvodyat-obyazatelnyy-laboratornyy-kontrol-palmovogo-masla-i-transzhirov/"/>
-    <hyperlink ref="L24" r:id="rId23" display="https://www.spot.uz/ru/2026/07/30/palm-oil"/>
-    <hyperlink ref="L25" r:id="rId24" display="https://vzglyad.uz/2026/10/09/obsuzhdenie-poryadka-markirovki-rastitelnogo-masla"/>
-    <hyperlink ref="L26" r:id="rId25" display="https://dairynews.today/kz/news/armenia-to-enforce-stricter-labeling-rules-for-dairy-and-meat-products.html"/>
+    <hyperlink ref="L10" r:id="rId9" display="https://base.spinform.ru/show_doc.fwx?rgn=177646"/>
+    <hyperlink ref="L11" r:id="rId10" display="https://adilet.zan.kz/rus/docs/H13EV000067"/>
+    <hyperlink ref="L12" r:id="rId11" display="https://biz.ligazakon.net/news/231710_prezident-pdpisav-zakon-pro-obmezhennya-vikoristannya-palmovo-ol-u-produktakh-kharchuvannya"/>
+    <hyperlink ref="L13" r:id="rId12" display="https://ngu.com.ua/palmova-oliia-shkoda-sklad-doza-i-etyketka/"/>
+    <hyperlink ref="L14" r:id="rId13" display="https://ansa.gov.md/sites/default/files/documents/Ordine/Ordin%20nr.%20369.pdf"/>
+    <hyperlink ref="L15" r:id="rId14" display="https://www.retail.ru/news/v-rossii-poyavilsya-edinyy-katalog-produktov-bez-palmy-23-dekabrya-2025-272975/"/>
+    <hyperlink ref="L16" r:id="rId15" display="https://www.v2b.ru/documents/federalnyy-zakon-ot-02-08-2019-268-fz/"/>
+    <hyperlink ref="L17" r:id="rId16" display="https://www.klerk.ru/buh/articles/713288/"/>
+    <hyperlink ref="L18" r:id="rId17" display="https://www.gazeta.ru/business/2019/07/01/12467725.shtml"/>
+    <hyperlink ref="L19" r:id="rId18" display="https://oleoscope.com/analytics/gosduma-predlozhila-markirovku-dlja-masla/"/>
+    <hyperlink ref="L20" r:id="rId19" display="https://ria.ru/20260722/markirovka-2106133235.html"/>
+    <hyperlink ref="L21" r:id="rId20" display="https://ria.ru/20261024/maslo-2126771171.html"/>
+    <hyperlink ref="L22" r:id="rId21" display="https://inbusiness.kz/ru/news/v-kazahstane-pochti-vdvoe-rasshirili-markirovku-tovarov"/>
+    <hyperlink ref="L23" r:id="rId22" display="https://kapital.kz/business/134274/maslopererabotchiki-rk-vystupayut-za-ukazaniye-nalichiya-v-produktakh-pal-movogo-masla.html"/>
+    <hyperlink ref="L24" r:id="rId23" display="https://dairynews.today/kz/news/v-kyrgyzstane-obsuzhdayut-ispolzovanie-palmovogo-masla-v-proizvodstve-moloka.html"/>
+    <hyperlink ref="L25" r:id="rId24" display="https://base.spinform.ru/show_doc.fwx?rgn=124770"/>
+    <hyperlink ref="L26" r:id="rId25" display="https://podrobno.uz/cat/obchestvo/v-uzbekistane-vvodyat-obyazatelnyy-laboratornyy-kontrol-palmovogo-masla-i-transzhirov/"/>
+    <hyperlink ref="L27" r:id="rId26" display="https://www.spot.uz/ru/2026/07/30/palm-oil"/>
+    <hyperlink ref="L28" r:id="rId27" display="https://vzglyad.uz/2026/10/09/obsuzhdenie-poryadka-markirovki-rastitelnogo-masla"/>
+    <hyperlink ref="L29" r:id="rId28" display="https://dairynews.today/kz/news/armenia-to-enforce-stricter-labeling-rules-for-dairy-and-meat-products.html"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3576,7 +3756,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId26"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
 
@@ -3594,32 +3774,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B1" s="12"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3628,7 +3808,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="B6" s="12"/>
     </row>
@@ -3646,7 +3826,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B9" s="12"/>
     </row>
@@ -3656,7 +3836,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="B11" s="12"/>
     </row>
@@ -3674,31 +3854,31 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="B18" s="12"/>
     </row>
@@ -3720,26 +3900,26 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
